--- a/artfynd/A 61074-2024 artfynd.xlsx
+++ b/artfynd/A 61074-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121792893</v>
+        <v>121792894</v>
       </c>
       <c r="B2" t="n">
         <v>94885</v>
@@ -708,7 +708,11 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>m²</t>
@@ -723,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609370</v>
+        <v>609275</v>
       </c>
       <c r="R2" t="n">
-        <v>6500433</v>
+        <v>6500248</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,12 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:57</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Område med riklig förekomst</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,7 +799,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121792894</v>
+        <v>121792893</v>
       </c>
       <c r="B3" t="n">
         <v>94885</v>
@@ -833,11 +832,7 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>m²</t>
@@ -852,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609275</v>
+        <v>609370</v>
       </c>
       <c r="R3" t="n">
-        <v>6500248</v>
+        <v>6500433</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +892,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Område med riklig förekomst</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 61074-2024 artfynd.xlsx
+++ b/artfynd/A 61074-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121792894</v>
+        <v>121792893</v>
       </c>
       <c r="B2" t="n">
         <v>94885</v>
@@ -708,11 +708,7 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>m²</t>
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609275</v>
+        <v>609370</v>
       </c>
       <c r="R2" t="n">
-        <v>6500248</v>
+        <v>6500433</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +768,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Område med riklig förekomst</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121792893</v>
+        <v>121792889</v>
       </c>
       <c r="B3" t="n">
-        <v>94885</v>
+        <v>57510</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,35 +812,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -847,13 +852,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609370</v>
+        <v>609396</v>
       </c>
       <c r="R3" t="n">
-        <v>6500433</v>
+        <v>6500460</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,12 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:57</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Område med riklig förekomst</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121792889</v>
+        <v>121792894</v>
       </c>
       <c r="B4" t="n">
-        <v>57510</v>
+        <v>94885</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,39 +936,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609396</v>
+        <v>609275</v>
       </c>
       <c r="R4" t="n">
-        <v>6500460</v>
+        <v>6500248</v>
       </c>
       <c r="S4" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 61074-2024 artfynd.xlsx
+++ b/artfynd/A 61074-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121792893</v>
+        <v>121792889</v>
       </c>
       <c r="B2" t="n">
-        <v>94885</v>
+        <v>57510</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609370</v>
+        <v>609396</v>
       </c>
       <c r="R2" t="n">
-        <v>6500433</v>
+        <v>6500460</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,12 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:57</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Område med riklig förekomst</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121792889</v>
+        <v>121792893</v>
       </c>
       <c r="B3" t="n">
-        <v>57510</v>
+        <v>94885</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,39 +811,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -852,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609396</v>
+        <v>609370</v>
       </c>
       <c r="R3" t="n">
-        <v>6500460</v>
+        <v>6500433</v>
       </c>
       <c r="S3" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +892,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Område med riklig förekomst</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 61074-2024 artfynd.xlsx
+++ b/artfynd/A 61074-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121792893</v>
+        <v>121792894</v>
       </c>
       <c r="B3" t="n">
         <v>94885</v>
@@ -832,7 +832,11 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>m²</t>
@@ -847,13 +851,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609370</v>
+        <v>609275</v>
       </c>
       <c r="R3" t="n">
-        <v>6500433</v>
+        <v>6500248</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,12 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:57</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Område med riklig förekomst</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,7 +923,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121792894</v>
+        <v>121792893</v>
       </c>
       <c r="B4" t="n">
         <v>94885</v>
@@ -957,11 +956,7 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>m²</t>
@@ -976,13 +971,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609275</v>
+        <v>609370</v>
       </c>
       <c r="R4" t="n">
-        <v>6500248</v>
+        <v>6500433</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1011,7 +1006,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1021,7 +1016,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Område med riklig förekomst</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 61074-2024 artfynd.xlsx
+++ b/artfynd/A 61074-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121792889</v>
+        <v>121792893</v>
       </c>
       <c r="B2" t="n">
-        <v>57510</v>
+        <v>94885</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609396</v>
+        <v>609370</v>
       </c>
       <c r="R2" t="n">
-        <v>6500460</v>
+        <v>6500433</v>
       </c>
       <c r="S2" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +768,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Område med riklig förekomst</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121792894</v>
+        <v>121792889</v>
       </c>
       <c r="B3" t="n">
-        <v>94885</v>
+        <v>57510</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,39 +812,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -851,13 +852,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609275</v>
+        <v>609396</v>
       </c>
       <c r="R3" t="n">
-        <v>6500248</v>
+        <v>6500460</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,7 +924,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121792893</v>
+        <v>121792894</v>
       </c>
       <c r="B4" t="n">
         <v>94885</v>
@@ -956,7 +957,11 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>m²</t>
@@ -971,13 +976,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609370</v>
+        <v>609275</v>
       </c>
       <c r="R4" t="n">
-        <v>6500433</v>
+        <v>6500248</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1006,7 +1011,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1016,12 +1021,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:57</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Område med riklig förekomst</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 61074-2024 artfynd.xlsx
+++ b/artfynd/A 61074-2024 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121792889</v>
+        <v>121792894</v>
       </c>
       <c r="B3" t="n">
-        <v>57510</v>
+        <v>94885</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,39 +812,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -852,13 +852,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609396</v>
+        <v>609275</v>
       </c>
       <c r="R3" t="n">
-        <v>6500460</v>
+        <v>6500248</v>
       </c>
       <c r="S3" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121792894</v>
+        <v>121792889</v>
       </c>
       <c r="B4" t="n">
-        <v>94885</v>
+        <v>57510</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,39 +936,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609275</v>
+        <v>609396</v>
       </c>
       <c r="R4" t="n">
-        <v>6500248</v>
+        <v>6500460</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 61074-2024 artfynd.xlsx
+++ b/artfynd/A 61074-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121792893</v>
       </c>
       <c r="B2" t="n">
-        <v>94885</v>
+        <v>94903</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121792894</v>
+        <v>121792889</v>
       </c>
       <c r="B3" t="n">
-        <v>94885</v>
+        <v>57518</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,39 +812,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -852,13 +852,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609275</v>
+        <v>609396</v>
       </c>
       <c r="R3" t="n">
-        <v>6500248</v>
+        <v>6500460</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121792889</v>
+        <v>121792894</v>
       </c>
       <c r="B4" t="n">
-        <v>57510</v>
+        <v>94903</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,39 +936,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609396</v>
+        <v>609275</v>
       </c>
       <c r="R4" t="n">
-        <v>6500460</v>
+        <v>6500248</v>
       </c>
       <c r="S4" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
